--- a/example data/25mm/Results/ID 15 - Run 3/ID 15 - Run 3 - Standard Devs. Stepcycle.xlsx
+++ b/example data/25mm/Results/ID 15 - Run 3/ID 15 - Run 3 - Standard Devs. Stepcycle.xlsx
@@ -425,181 +425,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AX26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SC Percentages</t>
+          <t>SC Percentage</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Nose x</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Nose y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ear base x</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ear base y</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Front paw tao x</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Front paw tao y</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Wrist x</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Wrist y</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Elbow x</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Elbow y</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Lower Shoulder x</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Lower Shoulder y</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Upper Shoulder x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Upper Shoulder y</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest x</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Iliac Crest y</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Hip x</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Hip y</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Knee x</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Knee y</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle x</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Ankle y</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao x</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Hind paw tao y</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tail base x</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Tail base y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tail center x</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Tail center y</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tail tip x</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Tail tip y</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Velocity</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Acceleration</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Velocity</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Acceleration</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Velocity</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Acceleration</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Velocity</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Acceleration</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Velocity</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Acceleration</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Velocity</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Acceleration</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Velocity</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Acceleration</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Velocity</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Acceleration</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Velocity</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Acceleration</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Velocity</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Acceleration</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle Velocity</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle Acceleration</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle Velocity</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle Acceleration</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle Velocity</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle Acceleration</t>
         </is>
@@ -610,106 +685,151 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3623787657589927</v>
+        <v>7.006847006756056</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1814934459120958</v>
+        <v>0.3623787657589922</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1570348944164477</v>
+        <v>5.760897093435453</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3977361164343655</v>
+        <v>0.1814934459120951</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8093522224235059</v>
+        <v>9.013147838717979</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3995465224113194</v>
+        <v>0.1570348944164543</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0692353749959989</v>
+        <v>9.85585509515518</v>
       </c>
       <c r="I2" t="n">
-        <v>1.784437885906096</v>
+        <v>0.3977361164343646</v>
       </c>
       <c r="J2" t="n">
-        <v>1.636520845461015</v>
+        <v>6.29402565335835</v>
       </c>
       <c r="K2" t="n">
-        <v>1.450664819517271</v>
+        <v>0.8093522224235075</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8455818123800338</v>
+        <v>5.863745804959345</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7618448946275705</v>
+        <v>0.3995465224113207</v>
       </c>
       <c r="N2" t="n">
-        <v>2.362382850578162</v>
+        <v>5.751452869581783</v>
       </c>
       <c r="O2" t="n">
-        <v>2.635622903401654</v>
+        <v>0.06923537499599923</v>
       </c>
       <c r="P2" t="n">
-        <v>17.75878778331946</v>
+        <v>6.601648633100647</v>
       </c>
       <c r="Q2" t="n">
-        <v>18.5203002119317</v>
+        <v>1.784437885906093</v>
       </c>
       <c r="R2" t="n">
-        <v>1.859855559512555</v>
+        <v>6.778668737847569</v>
       </c>
       <c r="S2" t="n">
-        <v>4.238730244123248</v>
+        <v>1.636520845461007</v>
       </c>
       <c r="T2" t="n">
+        <v>5.487890233996274</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.450664819517267</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4.359100162890267</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.8455818123800238</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.3032519019011374</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.7618448946275678</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6.123992321051225</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.362382850578157</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>7.627640451228425</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.635622903401663</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>61.46959737426879</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>17.75878778331947</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0.5696630313964037</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AG2" t="n">
         <v>0.5418228510189755</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AH2" t="n">
         <v>0.2958799132837818</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AI2" t="n">
         <v>0.3026310144869445</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AJ2" t="n">
         <v>0.6648368557723197</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AK2" t="n">
         <v>0.4274565640898471</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AL2" t="n">
         <v>0.5648096341849458</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AM2" t="n">
         <v>0.8055109718538606</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AN2" t="n">
         <v>0.4393631788845059</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AO2" t="n">
         <v>0.6705899723784371</v>
       </c>
-      <c r="AD2" t="n">
-        <v>1.611091732572481</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>5.3194328846025</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>3.385944215406484</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.690158055591631</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.2974582068082</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.883907859710261</v>
+      <c r="AP2" t="n">
+        <v>18.52030021193172</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.859855559512519</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.238730244123238</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.611091732572499</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.31943288460257</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.385944215406461</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.690158055591632</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.297458206808201</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2.883907859710308</v>
       </c>
     </row>
     <row r="3">
@@ -717,106 +837,151 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8724426848158245</v>
+        <v>7.075616769452108</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6305637246286581</v>
+        <v>0.8724426848158167</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2094619975604152</v>
+        <v>5.971523982806705</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6939270968223372</v>
+        <v>0.6305637246286574</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8082755268032286</v>
+        <v>10.40665350831595</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8706520668072182</v>
+        <v>0.2094619975604168</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5086843780048941</v>
+        <v>9.831080585279793</v>
       </c>
       <c r="I3" t="n">
-        <v>1.829199094480638</v>
+        <v>0.693927096822335</v>
       </c>
       <c r="J3" t="n">
-        <v>1.025579729891934</v>
+        <v>6.381037394119224</v>
       </c>
       <c r="K3" t="n">
-        <v>1.225786819330826</v>
+        <v>0.8082755268032319</v>
       </c>
       <c r="L3" t="n">
-        <v>1.99314592123814</v>
+        <v>5.779360892565664</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7300572376660653</v>
+        <v>0.8706520668072197</v>
       </c>
       <c r="N3" t="n">
+        <v>5.891118188062633</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5086843780048896</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6.407104641375823</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.829199094480635</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6.584147357149157</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.025579729891929</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.111862514078036</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.225786819330827</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.062420588422926</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.993145921238148</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.734300140772991</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.7300572376660642</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.366559053379495</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.784339922061462</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.437117458127061</v>
-      </c>
-      <c r="P3" t="n">
-        <v>14.57192337426195</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>8.295676600693728</v>
-      </c>
-      <c r="R3" t="n">
-        <v>9.829358900898329</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5.058168529315568</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="AB3" t="n">
+        <v>7.488189849358242</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.437117458127067</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>60.57165895312444</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>14.57192337426194</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0.8585753659886074</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AG3" t="n">
         <v>0.02948562574590725</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AH3" t="n">
         <v>0.5720362466746505</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AI3" t="n">
         <v>0.5278987707713029</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AJ3" t="n">
         <v>0.3470631427637032</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AK3" t="n">
         <v>0.1118894382822456</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AL3" t="n">
         <v>0.4303097800902651</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AM3" t="n">
         <v>0.2588626479046853</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AN3" t="n">
         <v>0.2671889042626106</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AO3" t="n">
         <v>0.2572354362252148</v>
       </c>
-      <c r="AD3" t="n">
-        <v>5.654438849469047</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.824106109419609</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>4.880387333332396</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.912460720258199</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.384088894320265</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.466373043535523</v>
+      <c r="AP3" t="n">
+        <v>8.295676600693712</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.829358900898294</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.058168529315596</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.654438849469061</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.824106109419634</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.880387333332421</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.912460720258178</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.384088894320242</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.466373043535545</v>
       </c>
     </row>
     <row r="4">
@@ -824,106 +989,151 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9714152870977223</v>
+        <v>7.661933688661809</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8165968147599644</v>
+        <v>0.9714152870977214</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1618042693124436</v>
+        <v>6.22264610666492</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4986121867312492</v>
+        <v>0.816596814759961</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9247176289646772</v>
+        <v>10.57496597225249</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0087454345044</v>
+        <v>0.1618042693124394</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7952197662234749</v>
+        <v>9.967596307852387</v>
       </c>
       <c r="I4" t="n">
-        <v>1.557234767949698</v>
+        <v>0.4986121867312465</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5651826858317602</v>
+        <v>6.66155537704263</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3906046968557188</v>
+        <v>0.9247176289646698</v>
       </c>
       <c r="L4" t="n">
-        <v>2.941225937393818</v>
+        <v>6.047468164280866</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4714449723842821</v>
+        <v>1.008745434504405</v>
       </c>
       <c r="N4" t="n">
-        <v>2.174315293740338</v>
+        <v>6.113837947595936</v>
       </c>
       <c r="O4" t="n">
-        <v>1.841476641359023</v>
+        <v>0.7952197662234696</v>
       </c>
       <c r="P4" t="n">
-        <v>7.291813326512623</v>
+        <v>5.765196944309968</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.925419696412527</v>
+        <v>1.55723476794969</v>
       </c>
       <c r="R4" t="n">
-        <v>15.8986908016573</v>
+        <v>5.690278098938204</v>
       </c>
       <c r="S4" t="n">
-        <v>6.432573768264586</v>
+        <v>0.5651826858317545</v>
       </c>
       <c r="T4" t="n">
+        <v>4.714411913865529</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.3906046968557197</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3.513354031006235</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.941225937393823</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.3668276900035</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4714449723842811</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.06289671705944</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.174315293740333</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.332962151131511</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.841476641359031</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>12.17199837440165</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>7.291813326512633</v>
+      </c>
+      <c r="AF4" t="n">
         <v>0.5679931203320016</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AG4" t="n">
         <v>0.2196188047768262</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AH4" t="n">
         <v>1.184889877726219</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AI4" t="n">
         <v>0.07432630800612453</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AJ4" t="n">
         <v>0.6093960393543473</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AK4" t="n">
         <v>0.1328857929876955</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AL4" t="n">
         <v>0.7003604418021973</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AM4" t="n">
         <v>0.1487495608323975</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AN4" t="n">
         <v>0.518709562147196</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AO4" t="n">
         <v>0.1129772305030501</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3.448581835600307</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.290613942249954</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>3.450969485839523</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.397131573007751</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3.709632403494118</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.076263796958988</v>
+      <c r="AP4" t="n">
+        <v>1.925419696412508</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>15.89869080165732</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6.432573768264606</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.448581835600288</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.2906139422499368</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.450969485839508</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.397131573007765</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.709632403494115</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.076263796958984</v>
       </c>
     </row>
     <row r="5">
@@ -931,106 +1141,151 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>1.283970571967305</v>
+        <v>8.536687143963526</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9967463109749796</v>
+        <v>1.283970571967296</v>
       </c>
       <c r="D5" t="n">
-        <v>0.306692225007859</v>
+        <v>6.482299398391015</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6180651714920384</v>
+        <v>0.996746310974981</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9317721917723552</v>
+        <v>10.50110297191672</v>
       </c>
       <c r="G5" t="n">
-        <v>1.018852627069555</v>
+        <v>0.3066922250078621</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8283175013427173</v>
+        <v>9.782554622447854</v>
       </c>
       <c r="I5" t="n">
-        <v>2.269917825913776</v>
+        <v>0.6180651714920391</v>
       </c>
       <c r="J5" t="n">
-        <v>1.223858697750546</v>
+        <v>7.444686645125602</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4518845233447337</v>
+        <v>0.9317721917723613</v>
       </c>
       <c r="L5" t="n">
-        <v>2.875892745968144</v>
+        <v>6.612688502662037</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6700514192599863</v>
+        <v>1.018852627069559</v>
       </c>
       <c r="N5" t="n">
-        <v>2.299258024222545</v>
+        <v>6.631992681850331</v>
       </c>
       <c r="O5" t="n">
-        <v>2.600517404647125</v>
+        <v>0.8283175013427195</v>
       </c>
       <c r="P5" t="n">
+        <v>4.786683920131344</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.269917825913771</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.583432631910645</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.223858697750544</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.020465005521163</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.4518845233447256</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.246121098160029</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.875892745968151</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.167592681006059</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.6700514192599885</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6.990502614420933</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.299258024222539</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7.269055784774488</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.60051740464713</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>57.68664649132785</v>
+      </c>
+      <c r="AE5" t="n">
         <v>15.50674804394299</v>
       </c>
-      <c r="Q5" t="n">
-        <v>6.396899136642904</v>
-      </c>
-      <c r="R5" t="n">
-        <v>19.66441118966653</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6.77608531519023</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="AF5" t="n">
         <v>0.6960094676353838</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AG5" t="n">
         <v>0.2088936716279014</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AH5" t="n">
         <v>0.925554843918011</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AI5" t="n">
         <v>0.2950996829614249</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AJ5" t="n">
         <v>0.6640032256095112</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AK5" t="n">
         <v>0.1427824948741495</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AL5" t="n">
         <v>0.9133651230175677</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AM5" t="n">
         <v>0.09883639534598886</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AN5" t="n">
         <v>0.7030689723051322</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AO5" t="n">
         <v>0.09396103537805044</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.874931229544447</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.779122946478404</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>3.264809451515533</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.555769549121096</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.651635745922954</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.1595739258805509</v>
+      <c r="AP5" t="n">
+        <v>6.396899136642885</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>19.66441118966655</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.776085315190246</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.874931229544432</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.779122946478397</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.264809451515561</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.555769549121115</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.65163574592299</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.1595739258805581</v>
       </c>
     </row>
     <row r="6">
@@ -1038,106 +1293,151 @@
         <v>20</v>
       </c>
       <c r="B6" t="n">
-        <v>1.474817507543626</v>
+        <v>8.744031497364112</v>
       </c>
       <c r="C6" t="n">
-        <v>1.191338411730835</v>
+        <v>1.474817507543623</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6974660193792934</v>
+        <v>6.915273196213803</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7269589548453662</v>
+        <v>1.191338411730844</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6579732969966684</v>
+        <v>10.49979537529159</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8469778595299212</v>
+        <v>0.6974660193792971</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6263810299021111</v>
+        <v>9.645566906337358</v>
       </c>
       <c r="I6" t="n">
-        <v>2.625551248724016</v>
+        <v>0.7269589548453698</v>
       </c>
       <c r="J6" t="n">
-        <v>1.68398121332798</v>
+        <v>7.202679749265681</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8248055360804142</v>
+        <v>0.6579732969966758</v>
       </c>
       <c r="L6" t="n">
-        <v>2.413405992571785</v>
+        <v>6.633624706034521</v>
       </c>
       <c r="M6" t="n">
+        <v>0.8469778595299272</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6.584341716930108</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.626381029902111</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.619807792807005</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.625551248724012</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4.631576720805315</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.683981213327971</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.537799470779212</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.8248055360804112</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.924650470816945</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.413405992571774</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.619155840871692</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.497589292115248</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.444593822199471</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.475576949836136</v>
-      </c>
-      <c r="P6" t="n">
-        <v>9.716656310055477</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>11.78505105657282</v>
-      </c>
-      <c r="R6" t="n">
-        <v>19.63653703588134</v>
-      </c>
-      <c r="S6" t="n">
-        <v>11.54757600148446</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="Z6" t="n">
+        <v>6.895133291498629</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.444593822199465</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.13143620766745</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.475576949836128</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>9.717989340279125</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.716656310055473</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.3429140800939821</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AG6" t="n">
         <v>1.159206318498142</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AH6" t="n">
         <v>0.491187913008002</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AI6" t="n">
         <v>0.8623108083246142</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AJ6" t="n">
         <v>0.3255193927890022</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AK6" t="n">
         <v>0.3488292118165527</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AL6" t="n">
         <v>0.2921942636993029</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AM6" t="n">
         <v>0.4906086281652692</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AN6" t="n">
         <v>0.2898933417574429</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AO6" t="n">
         <v>0.1434994591767604</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.867521731125807</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.743345815330588</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.174412426506735</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.161878696352871</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.9940975524943865</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.788824594723935</v>
+      <c r="AP6" t="n">
+        <v>11.78505105657285</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>19.63653703588128</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11.54757600148441</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.867521731125842</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.743345815330609</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.174412426506746</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.161878696352849</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.994097552494371</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.788824594723934</v>
       </c>
     </row>
     <row r="7">
@@ -1145,106 +1445,151 @@
         <v>24</v>
       </c>
       <c r="B7" t="n">
-        <v>1.712287351265636</v>
+        <v>8.950287231181132</v>
       </c>
       <c r="C7" t="n">
-        <v>1.418162881966116</v>
+        <v>1.712287351265634</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9525727903849307</v>
+        <v>7.411958553702434</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9708299259150721</v>
+        <v>1.418162881966111</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6302066254769746</v>
+        <v>10.47817885431375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9516815309989891</v>
+        <v>0.9525727903849286</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8688589185197328</v>
+        <v>9.395623155770748</v>
       </c>
       <c r="I7" t="n">
-        <v>2.161078081998046</v>
+        <v>0.9708299259150592</v>
       </c>
       <c r="J7" t="n">
-        <v>1.744699455580328</v>
+        <v>7.742448864862961</v>
       </c>
       <c r="K7" t="n">
-        <v>1.101808539964847</v>
+        <v>0.6302066254769692</v>
       </c>
       <c r="L7" t="n">
-        <v>2.079010521509062</v>
+        <v>6.974218319537632</v>
       </c>
       <c r="M7" t="n">
-        <v>2.476617312172416</v>
+        <v>0.9516815309989825</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68248840356344</v>
+        <v>7.090240350377088</v>
       </c>
       <c r="O7" t="n">
-        <v>4.038217968430887</v>
+        <v>0.8688589185197195</v>
       </c>
       <c r="P7" t="n">
-        <v>17.11314560460936</v>
+        <v>5.618045404542021</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.49232339187493</v>
+        <v>2.161078081998042</v>
       </c>
       <c r="R7" t="n">
+        <v>5.205233539180039</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.744699455580329</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.081610869450152</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.10180853996485</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.904194757314603</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.079010521509066</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.439910896487355</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.47661731217243</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7.322238093797511</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.682488403563434</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7.543877251030882</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.038217968430896</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>55.72972517844034</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>17.11314560460937</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.642661240934615</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.3402114750250714</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.125378441049766</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.2800678079515513</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.1652578956230668</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.04670013726886615</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1582544038624576</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.1686013460720591</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.4281142380648075</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.04613679708946482</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10.49232339187497</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>13.01084558400248</v>
       </c>
-      <c r="S7" t="n">
-        <v>9.955368313491627</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.642661240934615</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.3402114750250714</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.125378441049766</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.2800678079515513</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.1652578956230668</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.04670013726886615</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.1582544038624576</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.1686013460720591</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.4281142380648075</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.04613679708946482</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>4.014271724620727</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.992627296059691</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>4.25152310685203</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.140884978274572</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.6149948925942063</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.97926286261697</v>
+      <c r="AR7" t="n">
+        <v>9.955368313491645</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.014271724620753</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.992627296059706</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.251523106851977</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.14088497827458</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.6149948925942224</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.979262862616987</v>
       </c>
     </row>
     <row r="8">
@@ -1252,106 +1597,151 @@
         <v>28</v>
       </c>
       <c r="B8" t="n">
-        <v>1.672300940997052</v>
+        <v>8.85633918475264</v>
       </c>
       <c r="C8" t="n">
-        <v>1.178823417603151</v>
+        <v>1.672300940997064</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8910181860206763</v>
+        <v>7.697485527885034</v>
       </c>
       <c r="E8" t="n">
-        <v>1.092311117834604</v>
+        <v>1.178823417603155</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7108018352773177</v>
+        <v>10.01085411915112</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8524484351351643</v>
+        <v>0.8910181860206806</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6384301072991115</v>
+        <v>8.905359108789016</v>
       </c>
       <c r="I8" t="n">
-        <v>2.624735643206944</v>
+        <v>1.0923111178346</v>
       </c>
       <c r="J8" t="n">
-        <v>2.226889564808831</v>
+        <v>6.683917027017299</v>
       </c>
       <c r="K8" t="n">
-        <v>1.749488465735165</v>
+        <v>0.7108018352773241</v>
       </c>
       <c r="L8" t="n">
-        <v>1.726690314738443</v>
+        <v>6.705512978074123</v>
       </c>
       <c r="M8" t="n">
-        <v>2.623012689497416</v>
+        <v>0.8524484351351667</v>
       </c>
       <c r="N8" t="n">
-        <v>3.304646440325274</v>
+        <v>6.87998722194432</v>
       </c>
       <c r="O8" t="n">
-        <v>4.427899735097147</v>
+        <v>0.6384301072991126</v>
       </c>
       <c r="P8" t="n">
+        <v>5.847149376380539</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.624735643206937</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5.683351319219589</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.226889564808822</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.415895720713544</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.749488465735158</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.889390655164269</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.72669031473844</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.25580293801974</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.623012689497414</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7.787203006306236</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.304646440325264</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.009438095655486</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.427899735097136</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>8.900615985531013</v>
+      </c>
+      <c r="AE8" t="n">
         <v>9.195302836463622</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.8706216906984</v>
-      </c>
-      <c r="R8" t="n">
-        <v>9.132856385597824</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10.75236361007346</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="AF8" t="n">
         <v>0.913498445794834</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AG8" t="n">
         <v>0.1227025497025728</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AH8" t="n">
         <v>1.041966753891219</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AI8" t="n">
         <v>0.3007648609359659</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AJ8" t="n">
         <v>0.1837930169187715</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AK8" t="n">
         <v>0.3890484184053079</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AL8" t="n">
         <v>0.1567957852374746</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AM8" t="n">
         <v>0.3643934235619622</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AN8" t="n">
         <v>0.04793819406377315</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AO8" t="n">
         <v>0.4252665072876718</v>
       </c>
-      <c r="AD8" t="n">
-        <v>4.441121423715683</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.020439949550124</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>3.208386645337857</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.160247764829048</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.4525341997232956</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.287027395409285</v>
+      <c r="AP8" t="n">
+        <v>3.870621690698401</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.132856385597846</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10.75236361007349</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.441121423715703</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.020439949550116</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.20838664533788</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.16024776482907</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.4525341997232943</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.287027395409304</v>
       </c>
     </row>
     <row r="9">
@@ -1359,106 +1749,151 @@
         <v>32</v>
       </c>
       <c r="B9" t="n">
-        <v>1.715540071281024</v>
+        <v>10.04506190646336</v>
       </c>
       <c r="C9" t="n">
-        <v>1.223859547575141</v>
+        <v>1.71554007128103</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2491348432129141</v>
+        <v>8.334012777996762</v>
       </c>
       <c r="E9" t="n">
-        <v>0.763024023457461</v>
+        <v>1.223859547575142</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4026707262416226</v>
+        <v>9.292183593807835</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6124509158203235</v>
+        <v>0.2491348432129073</v>
       </c>
       <c r="H9" t="n">
+        <v>7.875221240559374</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.7630240234574649</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.669249680020567</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4026707262416185</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.63100803706628</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.6124509158203179</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8.188232618685532</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.4432504563771871</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.257386622072514</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.027436222670997</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.648809140323267</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.036125467208826</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.354180284518152</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.23818793219529</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
+        <v>6.91001148743</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.257386622072512</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6.563302333140056</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.027436222670998</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.142463377600314</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.648809140323268</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.043285319943411</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.03612546720882</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6.158694537540937</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.354180284518151</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8.240580796199271</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.238187932195302</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.696856712003354</v>
+      </c>
+      <c r="AC9" t="n">
         <v>4.04408069723013</v>
       </c>
-      <c r="P9" t="n">
-        <v>9.511148332978241</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>7.011779843834513</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3.760610835059399</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8.834010204171793</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="AD9" t="n">
+        <v>10.08291272376538</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.511148332978236</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.077442444006708</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AG9" t="n">
         <v>0.2405632505721612</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AH9" t="n">
         <v>1.11175419382601</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AI9" t="n">
         <v>0.4176375359260972</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AJ9" t="n">
         <v>0.6281769894686147</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AK9" t="n">
         <v>0.1805554595378617</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AL9" t="n">
         <v>0.5658884161312304</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AM9" t="n">
         <v>0.138327796313693</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AN9" t="n">
         <v>0.354368500411003</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AO9" t="n">
         <v>0.1817020732887322</v>
       </c>
-      <c r="AD9" t="n">
-        <v>4.286777019756333</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.06946755708762</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>3.420833808432258</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.641053607376872</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2.62045110597795</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.5301475230068594</v>
+      <c r="AP9" t="n">
+        <v>7.011779843834511</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.760610835059401</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.834010204171758</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.286777019756325</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.069467557087642</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.420833808432248</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.641053607376892</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.620451105977931</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.5301475230068347</v>
       </c>
     </row>
     <row r="10">
@@ -1466,106 +1901,151 @@
         <v>36</v>
       </c>
       <c r="B10" t="n">
-        <v>1.492516044401368</v>
+        <v>10.79272086360056</v>
       </c>
       <c r="C10" t="n">
-        <v>1.17378505404822</v>
+        <v>1.492516044401372</v>
       </c>
       <c r="D10" t="n">
-        <v>2.002142225440442</v>
+        <v>9.019997530027227</v>
       </c>
       <c r="E10" t="n">
-        <v>1.051659542599887</v>
+        <v>1.173785054048216</v>
       </c>
       <c r="F10" t="n">
-        <v>1.116142766626349</v>
+        <v>10.64189856024138</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8012530190791751</v>
+        <v>2.002142225440448</v>
       </c>
       <c r="H10" t="n">
-        <v>1.042745978176691</v>
+        <v>10.07439420658886</v>
       </c>
       <c r="I10" t="n">
-        <v>2.665388444648125</v>
+        <v>1.051659542599891</v>
       </c>
       <c r="J10" t="n">
-        <v>2.154366935457289</v>
+        <v>8.463313543695643</v>
       </c>
       <c r="K10" t="n">
+        <v>1.116142766626355</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8.575677323930595</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.8012530190791715</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.957020669331911</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.042745978176683</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7.960514719985675</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.66538844464813</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7.60596280603042</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.154366935457291</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7.297669738490578</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.965122472420869</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.669458177390899</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.7265516594756475</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.778693616890321</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.505292782029332</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="V10" t="n">
+        <v>7.89840121030422</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.6694581773908939</v>
+      </c>
+      <c r="X10" t="n">
+        <v>7.166080239940423</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.7265516594756454</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8.843390302028935</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.778693616890318</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.86773162818934</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.505292782029337</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>11.72947284493477</v>
+      </c>
+      <c r="AE10" t="n">
         <v>10.38083406964114</v>
       </c>
-      <c r="Q10" t="n">
-        <v>15.22254277063467</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7.445010992873302</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5.441637423118663</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="AF10" t="n">
         <v>0.4341978270893553</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AG10" t="n">
         <v>0.2868161635067513</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AH10" t="n">
         <v>0.2869528122256572</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AI10" t="n">
         <v>0.21630423863033</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AJ10" t="n">
         <v>0.3518107442428731</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AK10" t="n">
         <v>0.2011735844945703</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AL10" t="n">
         <v>0.3290667398952352</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AM10" t="n">
         <v>0.27845361807532</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AN10" t="n">
         <v>0.3579812049734836</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AO10" t="n">
         <v>0.2774723552619116</v>
       </c>
-      <c r="AD10" t="n">
-        <v>3.696489770758476</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.613769844661806</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.641293294029764</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.9499063646786058</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.892936376116275</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.180453194409988</v>
+      <c r="AP10" t="n">
+        <v>15.22254277063466</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7.445010992873307</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.441637423118718</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.696489770758471</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.613769844661805</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.641293294029772</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.9499063646785738</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.8929363761162643</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.180453194409961</v>
       </c>
     </row>
     <row r="11">
@@ -1573,106 +2053,151 @@
         <v>40</v>
       </c>
       <c r="B11" t="n">
-        <v>1.598992023837807</v>
+        <v>11.34134745731109</v>
       </c>
       <c r="C11" t="n">
-        <v>1.117285205165379</v>
+        <v>1.598992023837811</v>
       </c>
       <c r="D11" t="n">
-        <v>1.813097769109846</v>
+        <v>9.44040744813176</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9278321929156685</v>
+        <v>1.117285205165378</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9579700404298794</v>
+        <v>12.96679758063139</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8932563306213841</v>
+        <v>1.813097769109849</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7242002367904412</v>
+        <v>12.49901176846125</v>
       </c>
       <c r="I11" t="n">
+        <v>0.9278321929156693</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.718425038516604</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.9579700404298759</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8.037694150875566</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.8932563306213813</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8.723149712786947</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.724200236790435</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.990796571870228</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.945063369576683</v>
       </c>
-      <c r="J11" t="n">
-        <v>2.434799508487343</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.197149676004543</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.6166941134859242</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.9192274682863861</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.103361485720882</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.82100427547171</v>
-      </c>
-      <c r="P11" t="n">
-        <v>9.332940363168619</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>17.1319895501161</v>
-      </c>
       <c r="R11" t="n">
+        <v>7.843681167390195</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.434799508487342</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7.512714744860669</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.197149676004539</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.009845125716112</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6166941134859278</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7.447613378347928</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.9192274682863866</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>9.092413676494683</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.103361485720878</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10.79902165667075</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.821004275471704</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>12.51423216490146</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.332940363168616</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.2525979967815917</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.177218080123851</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.07486515278437204</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.02911661695843096</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.2054337248525755</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.1096376414240179</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.3115753927572418</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.1169467968879516</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.433644924873075</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.2774526313354996</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>17.13198955011609</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>10.1562093374759</v>
       </c>
-      <c r="S11" t="n">
-        <v>4.94051192976054</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.2525979967815917</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.177218080123851</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.07486515278437204</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.02911661695843096</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.2054337248525755</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.1096376414240179</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.3115753927572418</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.1169467968879516</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.433644924873075</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.2774526313354996</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.107098347683493</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.648865792527329</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.229273375388648</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.6083076101895093</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.4874953413548579</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.4691787094173624</v>
+      <c r="AR11" t="n">
+        <v>4.940511929760523</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.107098347683479</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.648865792527335</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.229273375388621</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.6083076101894973</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.4874953413548982</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.4691787094173589</v>
       </c>
     </row>
     <row r="12">
@@ -1680,106 +2205,151 @@
         <v>44</v>
       </c>
       <c r="B12" t="n">
+        <v>10.90882786978081</v>
+      </c>
+      <c r="C12" t="n">
         <v>1.107064406985601</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.847309895709762</v>
-      </c>
       <c r="D12" t="n">
-        <v>0.70998258781248</v>
+        <v>9.413032730849647</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7901141141871837</v>
+        <v>0.8473098957097606</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5294627064886572</v>
+        <v>12.45537263958738</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5844216080439627</v>
+        <v>0.7099825878124875</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4039174664207177</v>
+        <v>12.12572329913769</v>
       </c>
       <c r="I12" t="n">
-        <v>3.072998799078433</v>
+        <v>0.7901141141871917</v>
       </c>
       <c r="J12" t="n">
-        <v>2.618293970777203</v>
+        <v>7.524222338045052</v>
       </c>
       <c r="K12" t="n">
-        <v>2.114898775896406</v>
+        <v>0.52946270648866</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9525220810487569</v>
+        <v>7.734279193971505</v>
       </c>
       <c r="M12" t="n">
-        <v>1.38023972230464</v>
+        <v>0.584421608043961</v>
       </c>
       <c r="N12" t="n">
-        <v>4.356840057265144</v>
+        <v>8.118387061589956</v>
       </c>
       <c r="O12" t="n">
-        <v>2.394476364883316</v>
+        <v>0.4039174664207157</v>
       </c>
       <c r="P12" t="n">
-        <v>6.680908246088797</v>
+        <v>8.046339714326091</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.6829259213713</v>
+        <v>3.072998799078434</v>
       </c>
       <c r="R12" t="n">
-        <v>13.63411696285466</v>
+        <v>8.024632394659845</v>
       </c>
       <c r="S12" t="n">
-        <v>4.551632930844014</v>
+        <v>2.618293970777191</v>
       </c>
       <c r="T12" t="n">
+        <v>7.935452966088063</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.114898775896396</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.112013988516088</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.9525220810487504</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7.309331681031216</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.380239722304641</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>9.082393436762514</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.356840057265145</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.86742600800669</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.394476364883306</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12.55666712015914</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>6.680908246088806</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0.3024244302514568</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AG12" t="n">
         <v>0.08897177009632075</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AH12" t="n">
         <v>0.08887251581514433</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AI12" t="n">
         <v>0.05654307341874781</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AJ12" t="n">
         <v>0.1820506309607713</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AK12" t="n">
         <v>0.09230959458606837</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AL12" t="n">
         <v>0.5357895875824363</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AM12" t="n">
         <v>0.1724451311186643</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AN12" t="n">
         <v>0.6880858318143955</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AO12" t="n">
         <v>0.2715078421380556</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1.876633404995596</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.112164081373995</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.263728525221348</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.126364608992828</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.7292271636038156</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.431200762421154</v>
+      <c r="AP12" t="n">
+        <v>15.68292592137133</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13.63411696285463</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.551632930844011</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.876633404995594</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.1121640813739995</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.263728525221361</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.126364608992812</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.7292271636038283</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.431200762421146</v>
       </c>
     </row>
     <row r="13">
@@ -1787,106 +2357,151 @@
         <v>48</v>
       </c>
       <c r="B13" t="n">
-        <v>1.381214583151945</v>
+        <v>10.94671489917718</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6396004999425766</v>
+        <v>1.381214583151938</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9107461708224343</v>
+        <v>9.425797207086008</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8635240609704631</v>
+        <v>0.6396004999425826</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6327217470358291</v>
+        <v>12.8256384981313</v>
       </c>
       <c r="G13" t="n">
-        <v>0.420061071076873</v>
+        <v>0.9107461708224226</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2438602613281544</v>
+        <v>10.35968983593609</v>
       </c>
       <c r="I13" t="n">
-        <v>2.511843780420268</v>
+        <v>0.8635240609704639</v>
       </c>
       <c r="J13" t="n">
-        <v>2.222880601160806</v>
+        <v>8.443548393157004</v>
       </c>
       <c r="K13" t="n">
-        <v>1.941456217961949</v>
+        <v>0.6327217470358276</v>
       </c>
       <c r="L13" t="n">
+        <v>8.579041896244883</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.4200610710768636</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8.373310410103114</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.2438602613281604</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9.061573388832391</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.511843780420264</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8.505791731435647</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.22288060116081</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7.984509708452254</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.941456217961944</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8.277615711308794</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.365584457445363</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.414595408339432</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.53855995201311</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.107967730387753</v>
-      </c>
-      <c r="P13" t="n">
-        <v>5.096926559005902</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>13.72102489412942</v>
-      </c>
-      <c r="R13" t="n">
-        <v>12.70813155872123</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5.300779613888403</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="X13" t="n">
+        <v>7.367456696614608</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.414595408339424</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9.342337106815165</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.538559952013101</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>10.99183953798788</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.107967730387748</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12.195570591775</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>5.096926559005899</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0.0969036762540656</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AG13" t="n">
         <v>0.12076413087465</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AH13" t="n">
         <v>0.1677769413139191</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AI13" t="n">
         <v>0.07294999446688499</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AJ13" t="n">
         <v>0.1595692636262142</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AK13" t="n">
         <v>0.1892290817042985</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AL13" t="n">
         <v>0.5422820026473536</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AM13" t="n">
         <v>0.1845466169689896</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AN13" t="n">
         <v>0.494282788470603</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AO13" t="n">
         <v>0.5260561704165668</v>
       </c>
-      <c r="AD13" t="n">
-        <v>0.8702259561573911</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.4390671716055127</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.742324693776528</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.2010836606518693</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.299472854704675</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.370144397892592</v>
+      <c r="AP13" t="n">
+        <v>13.72102489412938</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>12.7081315587213</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.300779613888398</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.8702259561573695</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.4390671716055234</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.742324693776542</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.2010836606518397</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.299472854704662</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.370144397892596</v>
       </c>
     </row>
     <row r="14">
@@ -1894,106 +2509,151 @@
         <v>52</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7240830297779932</v>
+        <v>10.7283440189118</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2771814616054363</v>
+        <v>0.7240830297779954</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6192376975940537</v>
+        <v>9.457095146648435</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5012449522592547</v>
+        <v>0.2771814616054446</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4073427279593398</v>
+        <v>10.70336037983132</v>
       </c>
       <c r="G14" t="n">
-        <v>0.554650961240383</v>
+        <v>0.6192376975940608</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4526998177694882</v>
+        <v>9.766099648664891</v>
       </c>
       <c r="I14" t="n">
-        <v>2.836263595731245</v>
+        <v>0.5012449522592534</v>
       </c>
       <c r="J14" t="n">
-        <v>2.467271388883769</v>
+        <v>8.759357993669113</v>
       </c>
       <c r="K14" t="n">
-        <v>1.891054709847353</v>
+        <v>0.4073427279593405</v>
       </c>
       <c r="L14" t="n">
-        <v>2.500532161040668</v>
+        <v>8.660770001687174</v>
       </c>
       <c r="M14" t="n">
-        <v>1.625251913612228</v>
+        <v>0.5546509612403808</v>
       </c>
       <c r="N14" t="n">
+        <v>8.410778498926232</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.4526998177694923</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8.888545198621172</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.836263595731253</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8.892929637696151</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.467271388883773</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.993627511766829</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.891054709847359</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8.368952789016223</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.500532161040656</v>
+      </c>
+      <c r="X14" t="n">
+        <v>7.533286170051594</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.625251913612231</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9.358909417303897</v>
+      </c>
+      <c r="AA14" t="n">
         <v>4.218769771760285</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.886027520713299</v>
-      </c>
-      <c r="P14" t="n">
-        <v>4.062010063997112</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>13.37065867982448</v>
-      </c>
-      <c r="R14" t="n">
-        <v>15.32163035757933</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.231043576094669</v>
-      </c>
-      <c r="T14" t="n">
+      <c r="AB14" t="n">
+        <v>11.4291549880725</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.88602752071331</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12.06191387940934</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4.062010063997107</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.1721192156588273</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AG14" t="n">
         <v>0.02684045846694676</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AH14" t="n">
         <v>0.04573369906591703</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AI14" t="n">
         <v>0.2710601740827231</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AJ14" t="n">
         <v>0.4776681198615084</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AK14" t="n">
         <v>0.1704811841999252</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AL14" t="n">
         <v>0.5395603816406298</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AM14" t="n">
         <v>0.3368034084427264</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AN14" t="n">
         <v>0.6306093537814802</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AO14" t="n">
         <v>0.4047321696861679</v>
       </c>
-      <c r="AD14" t="n">
-        <v>1.331976719223287</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.115997124660557</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.378353087087233</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.358269211079409</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>3.300690470498338</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.839153515080899</v>
+      <c r="AP14" t="n">
+        <v>13.37065867982452</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>15.3216303575793</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.23104357609468</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.331976719223313</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.115997124660578</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.378353087087195</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.358269211079406</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3.300690470498359</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.839153515080883</v>
       </c>
     </row>
     <row r="15">
@@ -2001,106 +2661,151 @@
         <v>56</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5094287592162553</v>
+        <v>10.57319570408851</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6096243295146768</v>
+        <v>0.5094287592162603</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5913408560523196</v>
+        <v>9.350733438494299</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9517516237605675</v>
+        <v>0.6096243295146739</v>
       </c>
       <c r="F15" t="n">
-        <v>1.344560734562706</v>
+        <v>10.24964860679517</v>
       </c>
       <c r="G15" t="n">
-        <v>1.140728633812247</v>
+        <v>0.5913408560523202</v>
       </c>
       <c r="H15" t="n">
-        <v>1.136549735087128</v>
+        <v>9.316924686736179</v>
       </c>
       <c r="I15" t="n">
+        <v>0.9517516237605654</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8.832033068997124</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.344560734562696</v>
+      </c>
+      <c r="L15" t="n">
+        <v>8.818903213007655</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.140728633812236</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8.810146864148454</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.136549735087126</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8.073517263192352</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.881341840154833</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.424854915001982</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="R15" t="n">
+        <v>8.465381843075239</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.42485491500199</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7.949815657093306</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.857759003796194</v>
       </c>
-      <c r="L15" t="n">
-        <v>3.049759268873212</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.888148624002592</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.3614742665291</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.593992248958225</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.844007553317601</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>12.11481338174638</v>
-      </c>
-      <c r="R15" t="n">
-        <v>17.40751305449678</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.76919478294385</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
+        <v>8.426021090238855</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.049759268873204</v>
+      </c>
+      <c r="X15" t="n">
+        <v>7.692323400378823</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.888148624002591</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>9.831778148311777</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.361474266529098</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11.06845167830737</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.593992248958227</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12.44092526336734</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.84400755331759</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0.1038176006150424</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AG15" t="n">
         <v>0.126961498838795</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AH15" t="n">
         <v>0.4090540451392858</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AI15" t="n">
         <v>0.1419739250252858</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AJ15" t="n">
         <v>0.3788943320983258</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AK15" t="n">
         <v>0.16668709671695</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AL15" t="n">
         <v>0.3574907842608666</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AM15" t="n">
         <v>0.1970107814617442</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AN15" t="n">
         <v>0.3967888970273966</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AO15" t="n">
         <v>0.3111785075647867</v>
       </c>
-      <c r="AD15" t="n">
-        <v>3.492559111717974</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.441058726411378</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AP15" t="n">
+        <v>12.11481338174642</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>17.4075130544968</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.769194782943869</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.492559111717985</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.441058726411398</v>
+      </c>
+      <c r="AU15" t="n">
         <v>3.300385493293444</v>
       </c>
-      <c r="AG15" t="n">
-        <v>0.7090133305289074</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.942296922438965</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.590755029758981</v>
+      <c r="AV15" t="n">
+        <v>0.7090133305288803</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.942296922438951</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.590755029758974</v>
       </c>
     </row>
     <row r="16">
@@ -2108,106 +2813,151 @@
         <v>60</v>
       </c>
       <c r="B16" t="n">
-        <v>0.6019017582776864</v>
+        <v>10.52414316373588</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8667414022849738</v>
+        <v>0.6019017582776836</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9048220385449623</v>
+        <v>9.309608316991055</v>
       </c>
       <c r="E16" t="n">
-        <v>1.295957982067679</v>
+        <v>0.8667414022849665</v>
       </c>
       <c r="F16" t="n">
-        <v>1.920570142548522</v>
+        <v>9.478095320136648</v>
       </c>
       <c r="G16" t="n">
-        <v>1.468359533703796</v>
+        <v>0.904822038544963</v>
       </c>
       <c r="H16" t="n">
-        <v>1.412624534703232</v>
+        <v>9.262424858339015</v>
       </c>
       <c r="I16" t="n">
-        <v>2.982282583815594</v>
+        <v>1.295957982067672</v>
       </c>
       <c r="J16" t="n">
-        <v>2.080790298505761</v>
+        <v>8.823080450639425</v>
       </c>
       <c r="K16" t="n">
-        <v>1.321458978884561</v>
+        <v>1.920570142548519</v>
       </c>
       <c r="L16" t="n">
-        <v>3.169627675531638</v>
+        <v>8.650007451750554</v>
       </c>
       <c r="M16" t="n">
-        <v>1.418833078906225</v>
+        <v>1.468359533703794</v>
       </c>
       <c r="N16" t="n">
-        <v>4.277869702511663</v>
+        <v>8.442048689241322</v>
       </c>
       <c r="O16" t="n">
-        <v>1.205193784536326</v>
+        <v>1.412624534703227</v>
       </c>
       <c r="P16" t="n">
+        <v>8.263952443124907</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.982282583815596</v>
+      </c>
+      <c r="R16" t="n">
+        <v>8.525495998687679</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.08079029850575</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8.532009377493489</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.321458978884558</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.053332425758176</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.169627675531636</v>
+      </c>
+      <c r="X16" t="n">
+        <v>7.582235477140138</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.418833078906215</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>10.15597412018508</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.277869702511661</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11.52985415454267</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.20519378453633</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>12.61535711676181</v>
+      </c>
+      <c r="AE16" t="n">
         <v>4.636672483488096</v>
       </c>
-      <c r="Q16" t="n">
-        <v>5.048393097797793</v>
-      </c>
-      <c r="R16" t="n">
-        <v>21.34222042544008</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.559866616713129</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="AF16" t="n">
         <v>0.2459162882260124</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AG16" t="n">
         <v>0.1808953619516006</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AH16" t="n">
         <v>0.3109293379576937</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AI16" t="n">
         <v>0.09211124929043213</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AJ16" t="n">
         <v>0.2773886553827284</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AK16" t="n">
         <v>0.2604650344732409</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AL16" t="n">
         <v>0.2916051833004072</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AM16" t="n">
         <v>0.166790980986979</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AN16" t="n">
         <v>0.06916296853399649</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AO16" t="n">
         <v>0.2493437501744611</v>
       </c>
-      <c r="AD16" t="n">
-        <v>3.712994978093537</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.759602322870501</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.249519199909593</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.30848697328362</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0.6114380145449607</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.131919661861302</v>
+      <c r="AP16" t="n">
+        <v>5.048393097797784</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>21.34222042544004</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.5598666167131</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3.712994978093541</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.759602322870506</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.249519199909565</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.308486973283608</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.6114380145449749</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>2.131919661861267</v>
       </c>
     </row>
     <row r="17">
@@ -2215,106 +2965,151 @@
         <v>64</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8557387787607068</v>
+        <v>10.3082606118868</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9371832580435989</v>
+        <v>0.8557387787607098</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8118519954769227</v>
+        <v>9.065925791468009</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9897454095093985</v>
+        <v>0.9371832580436033</v>
       </c>
       <c r="F17" t="n">
-        <v>1.574364971955375</v>
+        <v>9.477559714782835</v>
       </c>
       <c r="G17" t="n">
-        <v>1.289085765921153</v>
+        <v>0.8118519954769255</v>
       </c>
       <c r="H17" t="n">
-        <v>1.13491661228044</v>
+        <v>9.229376887501934</v>
       </c>
       <c r="I17" t="n">
-        <v>3.069239451211041</v>
+        <v>0.9897454095094009</v>
       </c>
       <c r="J17" t="n">
-        <v>2.429502131444889</v>
+        <v>8.639279734541626</v>
       </c>
       <c r="K17" t="n">
-        <v>1.882582726619561</v>
+        <v>1.574364971955384</v>
       </c>
       <c r="L17" t="n">
-        <v>3.706691401307126</v>
+        <v>8.415526766073905</v>
       </c>
       <c r="M17" t="n">
-        <v>1.37192064553811</v>
+        <v>1.289085765921155</v>
       </c>
       <c r="N17" t="n">
-        <v>4.426035812279673</v>
+        <v>8.567186311273089</v>
       </c>
       <c r="O17" t="n">
-        <v>1.04699510621192</v>
+        <v>1.134916612280436</v>
       </c>
       <c r="P17" t="n">
-        <v>5.185969269380495</v>
+        <v>8.284684095788736</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.450495745379877</v>
+        <v>3.069239451211045</v>
       </c>
       <c r="R17" t="n">
-        <v>20.15791524443298</v>
+        <v>8.864215845079274</v>
       </c>
       <c r="S17" t="n">
-        <v>2.152917496452428</v>
+        <v>2.429502131444877</v>
       </c>
       <c r="T17" t="n">
+        <v>8.391451832315663</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.882582726619565</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.054510483886961</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.706691401307132</v>
+      </c>
+      <c r="X17" t="n">
+        <v>8.121738241271144</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.371920645538115</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>10.02187940242608</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.426035812279676</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>11.33297475917227</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.046995106211907</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12.86488781437053</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>5.185969269380496</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0.2700919013217496</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AG17" t="n">
         <v>0.187699311596166</v>
       </c>
-      <c r="V17" t="n">
+      <c r="AH17" t="n">
         <v>0.2236393329253138</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AI17" t="n">
         <v>0.08871071649795013</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AJ17" t="n">
         <v>0.3558727164058235</v>
       </c>
-      <c r="Y17" t="n">
-        <v>0.247365526037242</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AK17" t="n">
+        <v>0.2473655260372428</v>
+      </c>
+      <c r="AL17" t="n">
         <v>0.3440865857808486</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AM17" t="n">
         <v>0.2379138298781246</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AN17" t="n">
         <v>0.5403248970853706</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AO17" t="n">
         <v>0.07019837496609121</v>
       </c>
-      <c r="AD17" t="n">
-        <v>1.553886050657657</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.643538934636006</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.349001492576183</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.253806149724357</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.434547361482623</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.135543457104229</v>
+      <c r="AP17" t="n">
+        <v>2.450495745379898</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>20.15791524443296</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.152917496452475</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.553886050657656</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.643538934636</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.349001492576173</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.253806149724337</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.434547361482575</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.135543457104252</v>
       </c>
     </row>
     <row r="18">
@@ -2322,106 +3117,151 @@
         <v>68</v>
       </c>
       <c r="B18" t="n">
-        <v>0.7809083405778563</v>
+        <v>9.937557452563963</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070018279044445</v>
+        <v>0.7809083405778585</v>
       </c>
       <c r="D18" t="n">
-        <v>1.802457138709373</v>
+        <v>9.180271298398464</v>
       </c>
       <c r="E18" t="n">
+        <v>1.070018279044447</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.888864174454453</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.802457138709383</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9.414639484688943</v>
+      </c>
+      <c r="I18" t="n">
         <v>1.778926819722839</v>
       </c>
-      <c r="F18" t="n">
-        <v>1.700817275668523</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.385514512467043</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.021177335084533</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.484377251321146</v>
-      </c>
       <c r="J18" t="n">
-        <v>3.094715367874389</v>
+        <v>8.799152826662068</v>
       </c>
       <c r="K18" t="n">
-        <v>2.309854940653879</v>
+        <v>1.700817275668528</v>
       </c>
       <c r="L18" t="n">
-        <v>4.124119784369793</v>
+        <v>8.569444756656805</v>
       </c>
       <c r="M18" t="n">
-        <v>2.325363279778744</v>
+        <v>1.385514512467052</v>
       </c>
       <c r="N18" t="n">
-        <v>4.86920215259974</v>
+        <v>8.514743406339809</v>
       </c>
       <c r="O18" t="n">
+        <v>1.021177335084529</v>
+      </c>
+      <c r="P18" t="n">
+        <v>8.186974002292574</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.484377251321149</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8.651580699055611</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.094715367874382</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8.164511780326833</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.309854940653864</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.052968717935183</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.124119784369782</v>
+      </c>
+      <c r="X18" t="n">
+        <v>7.833513479744682</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.325363279778732</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>10.0015651343072</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.86920215259973</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>11.77332504314354</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.236600889413181</v>
       </c>
-      <c r="P18" t="n">
-        <v>5.429964234527345</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.279698238048478</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="AD18" t="n">
+        <v>13.05877627905472</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>5.429964234527351</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.218084629455567</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.1210508407425646</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.3915352079004412</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.06826612748278613</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.2645459183550605</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.1848470250302482</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.2465597367770554</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.159260056152478</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.05493182873696299</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.2739497292754623</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.279698238048466</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>14.90320933437706</v>
       </c>
-      <c r="S18" t="n">
-        <v>1.839779022856636</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.218084629455567</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.1210508407425646</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.3915352079004412</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.06826612748278613</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.2645459183550588</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.1848470250302481</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.2465597367770554</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.159260056152478</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.05493182873696299</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0.2739497292754623</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.068943329213571</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.7378197354363468</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>3.095722591093348</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.558004465639193</v>
-      </c>
-      <c r="AH18" t="n">
+      <c r="AR18" t="n">
+        <v>1.839779022856604</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.068943329213568</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.7378197354363399</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.095722591093356</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.558004465639206</v>
+      </c>
+      <c r="AW18" t="n">
         <v>2.000574639912753</v>
       </c>
-      <c r="AI18" t="n">
-        <v>0.7917027799182575</v>
+      <c r="AX18" t="n">
+        <v>0.791702779918268</v>
       </c>
     </row>
     <row r="19">
@@ -2429,106 +3269,151 @@
         <v>72</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5305231353855852</v>
+        <v>10.20648607698549</v>
       </c>
       <c r="C19" t="n">
-        <v>1.208399749382926</v>
+        <v>0.5305231353855931</v>
       </c>
       <c r="D19" t="n">
-        <v>2.147492121181906</v>
+        <v>8.89167113264147</v>
       </c>
       <c r="E19" t="n">
-        <v>1.956158492593374</v>
+        <v>1.20839974938292</v>
       </c>
       <c r="F19" t="n">
-        <v>1.587643091974054</v>
+        <v>9.39159196806413</v>
       </c>
       <c r="G19" t="n">
-        <v>1.259016926732051</v>
+        <v>2.147492121181897</v>
       </c>
       <c r="H19" t="n">
-        <v>1.197407677685867</v>
+        <v>9.465420813172022</v>
       </c>
       <c r="I19" t="n">
-        <v>3.425353497144195</v>
+        <v>1.956158492593365</v>
       </c>
       <c r="J19" t="n">
-        <v>3.037971011429716</v>
+        <v>9.485661190589738</v>
       </c>
       <c r="K19" t="n">
-        <v>2.042661875280444</v>
+        <v>1.58764309197405</v>
       </c>
       <c r="L19" t="n">
-        <v>3.053398720436184</v>
+        <v>8.999643703321007</v>
       </c>
       <c r="M19" t="n">
-        <v>2.21125505674434</v>
+        <v>1.259016926732045</v>
       </c>
       <c r="N19" t="n">
-        <v>4.614235444864582</v>
+        <v>8.761742897517442</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8573758210594155</v>
+        <v>1.197407677685859</v>
       </c>
       <c r="P19" t="n">
-        <v>6.073012676969029</v>
+        <v>8.369230895301733</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.948553486204674</v>
+        <v>3.425353497144206</v>
       </c>
       <c r="R19" t="n">
-        <v>11.81525488828147</v>
+        <v>8.672560504393275</v>
       </c>
       <c r="S19" t="n">
-        <v>3.165213535486059</v>
+        <v>3.037971011429721</v>
       </c>
       <c r="T19" t="n">
+        <v>8.367602664250981</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.042661875280457</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.911080974045374</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.053398720436174</v>
+      </c>
+      <c r="X19" t="n">
+        <v>7.759019111182433</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.211255056744348</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>9.967457547290984</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.614235444864584</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>11.26637907769953</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.8573758210594186</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12.81491824612343</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>6.073012676969021</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0.4825361882019722</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AG19" t="n">
         <v>0.2720032516030498</v>
       </c>
-      <c r="V19" t="n">
+      <c r="AH19" t="n">
         <v>0.2697512161307001</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AI19" t="n">
         <v>0.2121430239263419</v>
       </c>
-      <c r="X19" t="n">
-        <v>0.1642363030466837</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.1583941575220716</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AJ19" t="n">
+        <v>0.1642363030466854</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.158394157522072</v>
+      </c>
+      <c r="AL19" t="n">
         <v>0.01734556328772473</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AM19" t="n">
         <v>0.2401884862069048</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AN19" t="n">
         <v>0.138116883452246</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AO19" t="n">
         <v>0.1784521816886156</v>
       </c>
-      <c r="AD19" t="n">
-        <v>2.08617147630843</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.907230127529442</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AP19" t="n">
+        <v>1.948553486204649</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>11.81525488828145</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3.165213535486039</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.086171476308427</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.90723012752944</v>
+      </c>
+      <c r="AU19" t="n">
         <v>5.207804240424164</v>
       </c>
-      <c r="AG19" t="n">
-        <v>1.29159823907408</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3.603737934907302</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.469430319221513</v>
+      <c r="AV19" t="n">
+        <v>1.291598239074103</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.603737934907313</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>2.469430319221517</v>
       </c>
     </row>
     <row r="20">
@@ -2536,106 +3421,151 @@
         <v>76</v>
       </c>
       <c r="B20" t="n">
-        <v>0.7768621183146309</v>
+        <v>16.98336977187272</v>
       </c>
       <c r="C20" t="n">
-        <v>1.244743092581532</v>
+        <v>0.7768621183146192</v>
       </c>
       <c r="D20" t="n">
-        <v>2.107921384640488</v>
+        <v>9.08679805102563</v>
       </c>
       <c r="E20" t="n">
-        <v>1.854915678216394</v>
+        <v>1.244743092581539</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8637111412231212</v>
+        <v>9.024745896681257</v>
       </c>
       <c r="G20" t="n">
-        <v>1.052009811150763</v>
+        <v>2.107921384640495</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7071097833019477</v>
+        <v>9.184348933584747</v>
       </c>
       <c r="I20" t="n">
-        <v>3.125101217883671</v>
+        <v>1.854915678216396</v>
       </c>
       <c r="J20" t="n">
-        <v>2.75290668815696</v>
+        <v>9.252484044942703</v>
       </c>
       <c r="K20" t="n">
-        <v>2.142170099493049</v>
+        <v>0.8637111412231306</v>
       </c>
       <c r="L20" t="n">
-        <v>2.662594819737955</v>
+        <v>9.035212751839424</v>
       </c>
       <c r="M20" t="n">
-        <v>2.032263569117782</v>
+        <v>1.052009811150765</v>
       </c>
       <c r="N20" t="n">
-        <v>4.127944664911287</v>
+        <v>8.945312411663718</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6628023084756153</v>
+        <v>0.707109783301955</v>
       </c>
       <c r="P20" t="n">
-        <v>6.816012426299483</v>
+        <v>8.102105258244206</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.319596789093736</v>
+        <v>3.125101217883676</v>
       </c>
       <c r="R20" t="n">
-        <v>4.089171360731372</v>
+        <v>8.717549041351326</v>
       </c>
       <c r="S20" t="n">
-        <v>9.476954725788497</v>
+        <v>2.752906688156971</v>
       </c>
       <c r="T20" t="n">
+        <v>8.084850736573561</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.142170099493054</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.880085312618585</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.66259481973796</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8.642601632399614</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.032263569117777</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>9.548807613688625</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.127944664911299</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>11.00193787674156</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.6628023084756104</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>12.36042233609782</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>6.816012426299475</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0.3843195916558165</v>
       </c>
-      <c r="U20" t="n">
+      <c r="AG20" t="n">
         <v>0.285470423106417</v>
       </c>
-      <c r="V20" t="n">
+      <c r="AH20" t="n">
         <v>0.1533838854930012</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AI20" t="n">
         <v>0.08928291462857482</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AJ20" t="n">
         <v>0.2287352602223963</v>
       </c>
-      <c r="Y20" t="n">
-        <v>0.1208158297230972</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AK20" t="n">
+        <v>0.120815829723098</v>
+      </c>
+      <c r="AL20" t="n">
         <v>0.221855184405079</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AM20" t="n">
         <v>0.06053114487614027</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AN20" t="n">
         <v>0.1730244758299327</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0.2719896278949902</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AO20" t="n">
+        <v>0.271989627894991</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3.319596789093726</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4.089171360731355</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>9.476954725788474</v>
+      </c>
+      <c r="AS20" t="n">
         <v>2.417889394992657</v>
       </c>
-      <c r="AE20" t="n">
-        <v>0.642296319392169</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>4.348764611037659</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.149929838075774</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>3.39279776150238</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.60956576016201</v>
+      <c r="AT20" t="n">
+        <v>0.6422963193921474</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.348764611037653</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.14992983807577</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>3.392797761502397</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.609565760162014</v>
       </c>
     </row>
     <row r="21">
@@ -2643,106 +3573,151 @@
         <v>80</v>
       </c>
       <c r="B21" t="n">
-        <v>1.003475998017951</v>
+        <v>16.38808570695426</v>
       </c>
       <c r="C21" t="n">
-        <v>1.184513031890411</v>
+        <v>1.003475998017946</v>
       </c>
       <c r="D21" t="n">
-        <v>2.050277846055331</v>
+        <v>8.993927589384741</v>
       </c>
       <c r="E21" t="n">
-        <v>1.577027595795256</v>
+        <v>1.18451303189043</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4725563903341486</v>
+        <v>8.333333843917368</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8072433144688269</v>
+        <v>2.05027784605534</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6896988949710496</v>
+        <v>8.605810183221489</v>
       </c>
       <c r="I21" t="n">
-        <v>2.688922582995618</v>
+        <v>1.577027595795262</v>
       </c>
       <c r="J21" t="n">
-        <v>2.368779492455259</v>
+        <v>8.877556935358793</v>
       </c>
       <c r="K21" t="n">
-        <v>1.942605468631236</v>
+        <v>0.4725563903341645</v>
       </c>
       <c r="L21" t="n">
-        <v>2.132508330253044</v>
+        <v>8.629216575736388</v>
       </c>
       <c r="M21" t="n">
-        <v>2.063465250959585</v>
+        <v>0.8072433144688416</v>
       </c>
       <c r="N21" t="n">
-        <v>3.602575220790608</v>
+        <v>8.619456433263743</v>
       </c>
       <c r="O21" t="n">
-        <v>1.020617377346273</v>
+        <v>0.6896988949710602</v>
       </c>
       <c r="P21" t="n">
-        <v>7.052889714795151</v>
+        <v>8.478262187075238</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.56059839525657</v>
+        <v>2.688922582995622</v>
       </c>
       <c r="R21" t="n">
-        <v>3.42169972439528</v>
+        <v>8.690248717443406</v>
       </c>
       <c r="S21" t="n">
-        <v>6.983551037469447</v>
+        <v>2.368779492455266</v>
       </c>
       <c r="T21" t="n">
+        <v>7.9103533991116</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.942605468631243</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.606541991833633</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.132508330253046</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8.527266439939536</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.06346525095959</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>9.137653134179631</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.602575220790614</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>10.11381984185427</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.020617377346278</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>11.60062565506469</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>7.052889714795157</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0.1137922851717243</v>
       </c>
-      <c r="U21" t="n">
+      <c r="AG21" t="n">
         <v>0.2453370004394589</v>
       </c>
-      <c r="V21" t="n">
+      <c r="AH21" t="n">
         <v>0.3263144396322663</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AI21" t="n">
         <v>0.03662339454713295</v>
       </c>
-      <c r="X21" t="n">
-        <v>0.2561227972342105</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.1521176263906066</v>
-      </c>
-      <c r="Z21" t="n">
+      <c r="AJ21" t="n">
+        <v>0.2561227972342094</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.1521176263906081</v>
+      </c>
+      <c r="AL21" t="n">
         <v>0.1136901814010464</v>
       </c>
-      <c r="AA21" t="n">
-        <v>0.06328140662452167</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0.4118300691948215</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0.1833597314062027</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.854200972700024</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.34359572780972</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>3.091304497829382</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AM21" t="n">
+        <v>0.06328140662452196</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.4118300691948231</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.1833597314062019</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4.560598395256573</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.421699724395295</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>6.983551037469531</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.854200972700008</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.343595727809731</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.091304497829366</v>
+      </c>
+      <c r="AV21" t="n">
         <v>0.6049273746709519</v>
       </c>
-      <c r="AH21" t="n">
-        <v>1.391973846283843</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.430745150683294</v>
+      <c r="AW21" t="n">
+        <v>1.391973846283839</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.430745150683304</v>
       </c>
     </row>
     <row r="22">
@@ -2750,106 +3725,151 @@
         <v>84</v>
       </c>
       <c r="B22" t="n">
+        <v>16.32206734802684</v>
+      </c>
+      <c r="C22" t="n">
         <v>1.696718710014928</v>
       </c>
-      <c r="C22" t="n">
-        <v>1.164588622098778</v>
-      </c>
       <c r="D22" t="n">
-        <v>1.569642468885521</v>
+        <v>9.04954860487755</v>
       </c>
       <c r="E22" t="n">
-        <v>1.381575708013161</v>
+        <v>1.164588622098791</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2317745726869459</v>
+        <v>8.576621278250704</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6026307239966208</v>
+        <v>1.569642468885527</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3734696224540781</v>
+        <v>8.633629117773287</v>
       </c>
       <c r="I22" t="n">
-        <v>1.997166518928971</v>
+        <v>1.38157570801316</v>
       </c>
       <c r="J22" t="n">
-        <v>2.33287099723574</v>
+        <v>8.643388960498333</v>
       </c>
       <c r="K22" t="n">
-        <v>2.116310373533791</v>
+        <v>0.2317745726869429</v>
       </c>
       <c r="L22" t="n">
-        <v>2.163911292511891</v>
+        <v>8.456849286040754</v>
       </c>
       <c r="M22" t="n">
-        <v>2.243724924036751</v>
+        <v>0.602630723996633</v>
       </c>
       <c r="N22" t="n">
+        <v>8.396952815271657</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.3734696224540864</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8.833984638993256</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.997166518928986</v>
+      </c>
+      <c r="R22" t="n">
+        <v>8.941352730765743</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.332870997235738</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7.591432645785349</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.116310373533799</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.342108533023632</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.163911292511886</v>
+      </c>
+      <c r="X22" t="n">
+        <v>8.56180833422396</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.243724924036759</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8.664650793630472</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3.18405371548182</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.649819885752733</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7.281607619528588</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.313876591221606</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.259912548614731</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10.82727158575258</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="AB22" t="n">
+        <v>9.389256648078472</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.64981988575273</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>10.71670690115201</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>7.281607619528589</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0.1373042354709864</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AG22" t="n">
         <v>0.09381226827967848</v>
       </c>
-      <c r="V22" t="n">
+      <c r="AH22" t="n">
         <v>0.2259526952228446</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AI22" t="n">
         <v>0.1945487265123695</v>
       </c>
-      <c r="X22" t="n">
-        <v>0.1638552085891082</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.376558793889122</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.3368463464073622</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.1697589150325557</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.5396532935517367</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.2223120106447778</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.5771302419534642</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.730380561836926</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3.156315850350143</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.66862089038656</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.550183043962661</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.78562877218789</v>
+      <c r="AJ22" t="n">
+        <v>0.1638552085891112</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.3765587938891204</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.3368463464073632</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0.1697589150325553</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.5396532935517352</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.2223120106447781</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>6.31387659122162</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>2.25991254861471</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>10.82727158575254</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.5771302419534775</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.730380561836949</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.156315850350127</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.668620890386553</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.550183043962635</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.785628772187896</v>
       </c>
     </row>
     <row r="23">
@@ -2857,106 +3877,151 @@
         <v>88</v>
       </c>
       <c r="B23" t="n">
-        <v>1.591361999804978</v>
+        <v>17.61022866091622</v>
       </c>
       <c r="C23" t="n">
-        <v>0.88390383021827</v>
+        <v>1.591361999804976</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4066459644287178</v>
+        <v>9.239155649659898</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3605419184654322</v>
+        <v>0.8839038302182688</v>
       </c>
       <c r="F23" t="n">
-        <v>0.256723457416605</v>
+        <v>8.483479174724513</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3159616065865343</v>
+        <v>0.4066459644287309</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2991507715148615</v>
+        <v>8.302996543073455</v>
       </c>
       <c r="I23" t="n">
-        <v>2.142717469837505</v>
+        <v>0.3605419184654304</v>
       </c>
       <c r="J23" t="n">
-        <v>2.263905942711957</v>
+        <v>8.277619967726221</v>
       </c>
       <c r="K23" t="n">
-        <v>1.92889120070272</v>
+        <v>0.2567234574166028</v>
       </c>
       <c r="L23" t="n">
-        <v>2.403367884874851</v>
+        <v>8.455959038735754</v>
       </c>
       <c r="M23" t="n">
-        <v>2.278102076789746</v>
+        <v>0.3159616065865209</v>
       </c>
       <c r="N23" t="n">
-        <v>3.167951192293854</v>
+        <v>8.2459820234946</v>
       </c>
       <c r="O23" t="n">
-        <v>2.602898620224565</v>
+        <v>0.2991507715148555</v>
       </c>
       <c r="P23" t="n">
-        <v>7.911874534475792</v>
+        <v>8.922257157681988</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.739161616079206</v>
+        <v>2.142717469837504</v>
       </c>
       <c r="R23" t="n">
-        <v>3.851965257080805</v>
+        <v>8.6299536364648</v>
       </c>
       <c r="S23" t="n">
-        <v>9.782502227149527</v>
+        <v>2.26390594271195</v>
       </c>
       <c r="T23" t="n">
+        <v>7.965151545031335</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.928891200702716</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.155799867394932</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.403367884874853</v>
+      </c>
+      <c r="X23" t="n">
+        <v>8.330473549025864</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.27810207678975</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8.353855447613501</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.167951192293852</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>8.759964827663469</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.602898620224567</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>10.2243103685421</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>7.911874534475796</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0.1802790043794878</v>
       </c>
-      <c r="U23" t="n">
+      <c r="AG23" t="n">
         <v>0.1179283101616758</v>
       </c>
-      <c r="V23" t="n">
+      <c r="AH23" t="n">
         <v>0.1014473476215246</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AI23" t="n">
         <v>0.15146567782762</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AJ23" t="n">
         <v>0.6167313599392176</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0.08199919933632238</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.3550996013259781</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.06166855920941325</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AK23" t="n">
+        <v>0.08199919933631995</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.3550996013259767</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0.06166855920941379</v>
+      </c>
+      <c r="AN23" t="n">
         <v>0.4029989234984673</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0.3787205144285232</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.686592944029835</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.8318679441324739</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0.3843637441018137</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.187637081617872</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.267062330962522</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.30404882431153</v>
+      <c r="AO23" t="n">
+        <v>0.3787205144285223</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>4.739161616079174</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>3.85196525708077</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>9.78250222714955</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.686592944029868</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.8318679441324717</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.3843637441017902</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.187637081617892</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.267062330962541</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.304048824311557</v>
       </c>
     </row>
     <row r="24">
@@ -2964,106 +4029,151 @@
         <v>92</v>
       </c>
       <c r="B24" t="n">
-        <v>2.224582199966405</v>
+        <v>84.60230697663496</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7458479983138717</v>
+        <v>2.224582199966402</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4198123811175574</v>
+        <v>9.254383321052901</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3016600353141799</v>
+        <v>0.7458479983138617</v>
       </c>
       <c r="F24" t="n">
-        <v>0.258852156061638</v>
+        <v>8.361386148573269</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2458908499315252</v>
+        <v>0.4198123811175464</v>
       </c>
       <c r="H24" t="n">
-        <v>0.198840201457919</v>
+        <v>8.385913598631413</v>
       </c>
       <c r="I24" t="n">
-        <v>1.931692846507074</v>
+        <v>0.301660035314169</v>
       </c>
       <c r="J24" t="n">
-        <v>2.18143306979352</v>
+        <v>8.590227746421904</v>
       </c>
       <c r="K24" t="n">
-        <v>1.652502354638738</v>
+        <v>0.2588521560616416</v>
       </c>
       <c r="L24" t="n">
-        <v>1.990609023699035</v>
+        <v>8.470481852969325</v>
       </c>
       <c r="M24" t="n">
-        <v>2.141434545152997</v>
+        <v>0.2458908499315094</v>
       </c>
       <c r="N24" t="n">
-        <v>3.048516806938086</v>
+        <v>8.520040452800361</v>
       </c>
       <c r="O24" t="n">
-        <v>3.371088953249942</v>
+        <v>0.1988402014579089</v>
       </c>
       <c r="P24" t="n">
-        <v>9.538169713227715</v>
+        <v>8.840036087664778</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.711106900198618</v>
+        <v>1.931692846507069</v>
       </c>
       <c r="R24" t="n">
-        <v>2.132730245621242</v>
+        <v>9.056099018649281</v>
       </c>
       <c r="S24" t="n">
-        <v>7.170682567289231</v>
+        <v>2.181433069793514</v>
       </c>
       <c r="T24" t="n">
+        <v>8.417245540157353</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.652502354638735</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.32945850057507</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.990609023699036</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8.203060501287412</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.141434545152996</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8.308667061989533</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.048516806938083</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.330846460064286</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.371088953249944</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>10.18285258583977</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.53816971322772</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0.09983525421671925</v>
       </c>
-      <c r="U24" t="n">
+      <c r="AG24" t="n">
         <v>0.1222084538075584</v>
       </c>
-      <c r="V24" t="n">
+      <c r="AH24" t="n">
         <v>0.2372732044293011</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AI24" t="n">
         <v>0.1785530979453133</v>
       </c>
-      <c r="X24" t="n">
-        <v>0.3238920051372577</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.3739312606983512</v>
-      </c>
-      <c r="Z24" t="n">
+      <c r="AJ24" t="n">
+        <v>0.323892005137255</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.3739312606983528</v>
+      </c>
+      <c r="AL24" t="n">
         <v>0.3777132332070834</v>
       </c>
-      <c r="AA24" t="n">
-        <v>0.2177081906883402</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AM24" t="n">
+        <v>0.2177081906883394</v>
+      </c>
+      <c r="AN24" t="n">
         <v>0.3167091151200413</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AO24" t="n">
         <v>0.2334980259111141</v>
       </c>
-      <c r="AD24" t="n">
-        <v>2.234978988366497</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.872994608373783</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.93668978812688</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.010022536236452</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>4.150231947804743</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.633692857827674</v>
+      <c r="AP24" t="n">
+        <v>5.711106900198625</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>2.132730245621172</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>7.170682567289153</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.234978988366509</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.872994608373813</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.936689788126921</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.010022536236468</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.150231947804774</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.63369285782769</v>
       </c>
     </row>
     <row r="25">
@@ -3071,106 +4181,151 @@
         <v>96</v>
       </c>
       <c r="B25" t="n">
-        <v>1.24034401226737</v>
+        <v>83.99098965328946</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8363587567810703</v>
+        <v>1.24034401226738</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4260654750805356</v>
+        <v>9.102235802111457</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3058921336021377</v>
+        <v>0.8363587567810707</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2989131674544741</v>
+        <v>8.329464118485397</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3958912867743354</v>
+        <v>0.4260654750805429</v>
       </c>
       <c r="H25" t="n">
-        <v>0.174950919162299</v>
+        <v>8.294646385736948</v>
       </c>
       <c r="I25" t="n">
-        <v>1.917060933133963</v>
+        <v>0.305892133602136</v>
       </c>
       <c r="J25" t="n">
-        <v>1.666270718417841</v>
+        <v>8.733313686231497</v>
       </c>
       <c r="K25" t="n">
-        <v>1.897501069897531</v>
+        <v>0.2989131674544749</v>
       </c>
       <c r="L25" t="n">
-        <v>1.541861204964024</v>
+        <v>8.230657522369947</v>
       </c>
       <c r="M25" t="n">
-        <v>2.21866085538952</v>
+        <v>0.3958912867743305</v>
       </c>
       <c r="N25" t="n">
-        <v>3.026126503302677</v>
+        <v>7.978723743066096</v>
       </c>
       <c r="O25" t="n">
-        <v>3.618621394961414</v>
+        <v>0.1749509191622994</v>
       </c>
       <c r="P25" t="n">
-        <v>10.63420567325171</v>
+        <v>8.291146349153289</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.995321260323967</v>
+        <v>1.917060933133969</v>
       </c>
       <c r="R25" t="n">
-        <v>7.598613520876791</v>
+        <v>8.380246185577098</v>
       </c>
       <c r="S25" t="n">
-        <v>17.62749300480793</v>
+        <v>1.666270718417846</v>
       </c>
       <c r="T25" t="n">
+        <v>8.012492088042091</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.897501069897535</v>
+      </c>
+      <c r="V25" t="n">
+        <v>7.067490580235354</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.541861204964018</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8.441013167435687</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.218660855389512</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7.825345070231686</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.026126503302679</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.443886586104052</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.618621394961412</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>10.23720287627373</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>10.6342056732517</v>
+      </c>
+      <c r="AF25" t="n">
         <v>0.06977156217292807</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AG25" t="n">
         <v>0.09001452373189421</v>
       </c>
-      <c r="V25" t="n">
+      <c r="AH25" t="n">
         <v>0.2761321735185923</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AI25" t="n">
         <v>0.07345931961724572</v>
       </c>
-      <c r="X25" t="n">
-        <v>0.1921158777479839</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.0718838709569166</v>
-      </c>
-      <c r="Z25" t="n">
+      <c r="AJ25" t="n">
+        <v>0.1921158777479858</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.07188387095691526</v>
+      </c>
+      <c r="AL25" t="n">
         <v>0.3160483161322853</v>
       </c>
-      <c r="AA25" t="n">
-        <v>0.4006281223103565</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="AM25" t="n">
+        <v>0.4006281223103579</v>
+      </c>
+      <c r="AN25" t="n">
         <v>0.2037458954384499</v>
       </c>
-      <c r="AC25" t="n">
-        <v>0.2295405915604087</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.500514096948407</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.177650637678916</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.86250652907461</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.238644787520517</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.139243657969191</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.476885419919324</v>
+      <c r="AO25" t="n">
+        <v>0.2295405915604115</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>6.995321260323957</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>7.598613520876824</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>17.62749300480802</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.500514096948431</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.177650637678934</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.862506529074638</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.238644787520555</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.139243657969193</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>5.476885419919407</v>
       </c>
     </row>
     <row r="26">
@@ -3178,106 +4333,151 @@
         <v>100</v>
       </c>
       <c r="B26" t="n">
-        <v>2.668675759923264</v>
+        <v>43.73390876113169</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5155858665077292</v>
+        <v>2.668675759923265</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3790142129755119</v>
+        <v>9.231471058192248</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2387806316665678</v>
+        <v>0.5155858665077301</v>
       </c>
       <c r="F26" t="n">
-        <v>0.257956439171233</v>
+        <v>8.376962187240906</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2789442980807464</v>
+        <v>0.37901421297551</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02873155811866542</v>
+        <v>8.245535564829748</v>
       </c>
       <c r="I26" t="n">
-        <v>2.400800399382366</v>
+        <v>0.2387806316665702</v>
       </c>
       <c r="J26" t="n">
-        <v>1.500725334403671</v>
+        <v>7.922556700793185</v>
       </c>
       <c r="K26" t="n">
-        <v>1.894120002872681</v>
+        <v>0.2579564391712261</v>
       </c>
       <c r="L26" t="n">
-        <v>1.554939195408686</v>
+        <v>8.2049481848813</v>
       </c>
       <c r="M26" t="n">
-        <v>1.825244408022726</v>
+        <v>0.2789442980807417</v>
       </c>
       <c r="N26" t="n">
-        <v>3.055032072697899</v>
+        <v>7.724372090107</v>
       </c>
       <c r="O26" t="n">
-        <v>3.517335033273229</v>
+        <v>0.0287315581186589</v>
       </c>
       <c r="P26" t="n">
+        <v>8.43278033370812</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.400800399382377</v>
+      </c>
+      <c r="R26" t="n">
+        <v>8.468401621279213</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.500725334403677</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8.037336392404294</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.894120002872687</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.985725723839984</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.554939195408688</v>
+      </c>
+      <c r="X26" t="n">
+        <v>8.32032439015248</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.82524440802273</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>7.594528854945158</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.055032072697914</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>8.449400903905508</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.517335033273235</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>9.819353681126213</v>
+      </c>
+      <c r="AE26" t="n">
         <v>11.39767700752755</v>
       </c>
-      <c r="Q26" t="n">
-        <v>7.825344706368559</v>
-      </c>
-      <c r="R26" t="n">
-        <v>5.7796679315027</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10.85341842759876</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="AF26" t="n">
         <v>0.1305032897571687</v>
       </c>
-      <c r="U26" t="n">
+      <c r="AG26" t="n">
         <v>0.1797766770978841</v>
       </c>
-      <c r="V26" t="n">
+      <c r="AH26" t="n">
         <v>0.1256910013631584</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AI26" t="n">
         <v>0.1508587574416754</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AJ26" t="n">
         <v>0.1801622561060616</v>
       </c>
-      <c r="Y26" t="n">
-        <v>0.2628202346810081</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0.4247592399697986</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.6612315817956161</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.1423829907851262</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.3459413616422133</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.059610031561414</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0.4412663532872533</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.683782063539704</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.889126502304406</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>6.830269425463684</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>8.914888853132991</v>
+      <c r="AK26" t="n">
+        <v>0.2628202346810113</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.4247592399698016</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.6612315817956167</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.1423829907851318</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.3459413616422188</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>7.825344706368575</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>5.779667931502702</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>10.8534184275987</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.059610031561458</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.4412663532872326</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.683782063539734</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.889126502304479</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>6.830269425463819</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>8.914888853133128</v>
       </c>
     </row>
   </sheetData>
